--- a/backend/src/main/resources/templates/trimestriel/DNS_OMSI.xlsx
+++ b/backend/src/main/resources/templates/trimestriel/DNS_OMSI.xlsx
@@ -1601,10 +1601,10 @@
   <dimension ref="A2:O49"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.86"/>
+    <col min="2" max="2" customWidth="true" hidden="false" style="1" width="20.14" collapsed="false" outlineLevel="0"/>
+    <col min="3" max="6" customWidth="true" hidden="false" style="1" width="15.14" collapsed="false" outlineLevel="0"/>
+    <col min="9" max="9" customWidth="true" hidden="false" style="1" width="11.71" collapsed="false" outlineLevel="0"/>
+    <col min="11" max="11" customWidth="true" hidden="false" style="1" width="13.86" collapsed="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2003,18 +2003,18 @@
   <dimension ref="A1:W1048576"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="4.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="1" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="1" width="12.57"/>
+    <col min="1" max="2" customWidth="true" hidden="false" style="1" width="4.14" collapsed="false" outlineLevel="0"/>
+    <col min="3" max="3" customWidth="true" hidden="false" style="1" width="19.71" collapsed="false" outlineLevel="0"/>
+    <col min="4" max="4" customWidth="true" hidden="false" style="1" width="21.71" collapsed="false" outlineLevel="0"/>
+    <col min="5" max="5" customWidth="true" hidden="false" style="1" width="7.29" collapsed="false" outlineLevel="0"/>
+    <col min="6" max="6" customWidth="true" hidden="false" style="1" width="18.86" collapsed="false" outlineLevel="0"/>
+    <col min="7" max="7" customWidth="true" hidden="false" style="1" width="11.29" collapsed="false" outlineLevel="0"/>
+    <col min="8" max="8" customWidth="true" hidden="false" style="1" width="13.29" collapsed="false" outlineLevel="0"/>
+    <col min="9" max="12" customWidth="true" hidden="false" style="1" width="17.71" collapsed="false" outlineLevel="0"/>
+    <col min="13" max="15" customWidth="true" hidden="false" style="1" width="13.29" collapsed="false" outlineLevel="0"/>
+    <col min="17" max="17" customWidth="true" hidden="false" style="1" width="12.42" collapsed="false" outlineLevel="0"/>
+    <col min="18" max="19" customWidth="true" hidden="false" style="1" width="11.29" collapsed="false" outlineLevel="0"/>
+    <col min="20" max="22" customWidth="true" hidden="false" style="1" width="12.57" collapsed="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
